--- a/reports/Debug-purgatory-20260106/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/Month to Date (Actual)_Visits.xlsx
@@ -437,7 +437,7 @@
         <v>46023</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C3" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C4" s="2">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>1445</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46026</v>
+        <v>46028</v>
       </c>
       <c r="C7" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C8" s="2">
-        <v>564</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -535,10 +535,10 @@
         <v>46023</v>
       </c>
       <c r="C9" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -549,10 +549,10 @@
         <v>46023</v>
       </c>
       <c r="C10" s="2">
-        <v>1552</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>1445</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C12" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,7 +591,7 @@
         <v>46026</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C14" s="2">
-        <v>19</v>
+        <v>564</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C15" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C16" s="2">
-        <v>322</v>
+        <v>1552</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="C17" s="2">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>46023</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C19" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C20" s="2">
-        <v>1455</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C21" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C22" s="2">
-        <v>18</v>
+        <v>322</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C25" s="2">
-        <v>6</v>
+        <v>608</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C27" s="2">
-        <v>1407</v>
+        <v>110</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C28" s="2">
-        <v>48</v>
+        <v>1469</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C29" s="2">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>906</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,7 +840,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C32" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C34" s="2">
-        <v>2</v>
+        <v>568</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C35" s="2">
-        <v>310</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C36" s="2">
-        <v>1099</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C40" s="2">
-        <v>1416</v>
+        <v>310</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C41" s="2">
-        <v>56</v>
+        <v>1099</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C44" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C45" s="2">
-        <v>89</v>
+        <v>1415</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C46" s="2">
-        <v>406</v>
+        <v>528</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>936</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C49" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C50" s="2">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C51" s="2">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C52" s="2">
-        <v>528</v>
+        <v>969</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C53" s="2">
-        <v>936</v>
+        <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C54" s="2">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1190,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C56" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C57" s="2">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C58" s="2">
-        <v>969</v>
+        <v>21</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C59" s="2">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C60" s="2">
-        <v>4</v>
+        <v>406</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C62" s="2">
-        <v>608</v>
+        <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C63" s="2">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C64" s="2">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C65" s="2">
-        <v>1469</v>
+        <v>258</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C66" s="2">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C67" s="2">
-        <v>906</v>
+        <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>1455</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,10 +1372,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C69" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C70" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C71" s="2">
-        <v>568</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C72" s="2">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C73" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C74" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C75" s="2">
-        <v>12</v>
+        <v>1407</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1473,7 +1473,7 @@
         <v>46027</v>
       </c>
       <c r="C76" s="2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C77" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1501,7 +1501,7 @@
         <v>46028</v>
       </c>
       <c r="C78" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>5</v>
